--- a/assets/upload/import_data.xlsx
+++ b/assets/upload/import_data.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="32">
   <si>
     <t>INDEK</t>
   </si>
@@ -58,6 +58,60 @@
   </si>
   <si>
     <t>UNIT KERJA PENCIPTA</t>
+  </si>
+  <si>
+    <t>KEPBUP</t>
+  </si>
+  <si>
+    <t>Nomor : 503.442/ 004/ BPMPP/ 2011. Tentang izin Apotik an. WIRA EKA FITRI</t>
+  </si>
+  <si>
+    <t>BPMPP</t>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>Nomor : 503. IMB/SK.080/BPMPP Tentang Izin Mendirikan Bangunan an. WARTA SUGIRA</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>Nomor : 503.IT/ SK. 025. BPMPP/2010. an Witana</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>Nomor : 503. IG/SK. 085-BPMPP/2011. Tentang Izin Gangguan an. Ir WIRANTO.M.Si</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>Nomor : 503. Pan/ Herr. 006-BPMPP/ 2009. Tentang IzinUsaha Kepariwisataan an. WIWIN WINARTI</t>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
+    <t>Nomor : 503. IMB/ SK. 120/ BPMPP/ 2011 Tentang IMB an. HJ. YUYU YUSANTI</t>
+  </si>
+  <si>
+    <t>Nomor : 503 : IMB/ SK.174/BPMPP/ 2011.Tentang IMB an. YOYO SUTARYO</t>
+  </si>
+  <si>
+    <t>Nomor : 503.IMB/ SK.153/ BPMPP/ 2011. Tentang IMB an. YADI SUKMAYADI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nomor : 503. IMB/ SK.154/ BPMPP/ 2011.Tentang IMB an. YANSOMA </t>
+  </si>
+  <si>
+    <t>Nomor : 503. IG/ SK. 165-BPMPP/ 2011. Tentang Ijin Gangguan an. YAYAN SAEFUDIN</t>
+  </si>
+  <si>
+    <t>Depo Baru</t>
   </si>
 </sst>
 </file>
@@ -89,7 +143,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -138,11 +192,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -161,6 +235,43 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -463,7 +574,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.5546875" bestFit="1" customWidth="1"/>
@@ -529,42 +640,310 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
+      <c r="B3" s="9">
+        <v>500</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="9">
+        <v>2011</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="12"/>
+      <c r="K3" s="13"/>
+      <c r="L3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="7">
+        <v>1</v>
+      </c>
+      <c r="B4" s="15">
+        <v>500</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="15">
+        <v>2011</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="I4" s="14"/>
+      <c r="J4" s="18"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="7">
+        <v>1</v>
+      </c>
+      <c r="B5" s="15">
+        <v>500</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="15">
+        <v>2010</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="14"/>
+      <c r="J5" s="18"/>
+      <c r="K5" s="19"/>
+      <c r="L5" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="7">
+        <v>1</v>
+      </c>
+      <c r="B6" s="15">
+        <v>500</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="15">
+        <v>2011</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="I6" s="14"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="7">
+        <v>1</v>
+      </c>
+      <c r="B7" s="15">
+        <v>500</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="15">
+        <v>2009</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="14"/>
+      <c r="H7" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="I7" s="14"/>
+      <c r="J7" s="18"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="7">
+        <v>1</v>
+      </c>
+      <c r="B8" s="15">
+        <v>500</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="15">
+        <v>2011</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="I8" s="14"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="19"/>
+      <c r="L8" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="7">
+        <v>1</v>
+      </c>
+      <c r="B9" s="15">
+        <v>500</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="15">
+        <v>2001</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="I9" s="15"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="7">
+        <v>1</v>
+      </c>
+      <c r="B10" s="15">
+        <v>500</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" s="15">
+        <v>2011</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" s="14"/>
+      <c r="H10" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10" s="15"/>
+      <c r="J10" s="18"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A11" s="7">
+        <v>1</v>
+      </c>
+      <c r="B11" s="15">
+        <v>500</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="15">
+        <v>2011</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="I11" s="15"/>
+      <c r="J11" s="18"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="7">
+        <v>1</v>
+      </c>
+      <c r="B12" s="15">
+        <v>500</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" s="15">
+        <v>2011</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" s="15"/>
+      <c r="J12" s="18"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="7" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/assets/upload/import_data.xlsx
+++ b/assets/upload/import_data.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="24" windowWidth="22980" windowHeight="9816"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7605"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
   <si>
     <t>INDEK</t>
   </si>
@@ -60,6 +65,9 @@
     <t>UNIT KERJA PENCIPTA</t>
   </si>
   <si>
+    <t>19</t>
+  </si>
+  <si>
     <t>KEPBUP</t>
   </si>
   <si>
@@ -70,48 +78,6 @@
   </si>
   <si>
     <t>01</t>
-  </si>
-  <si>
-    <t>Nomor : 503. IMB/SK.080/BPMPP Tentang Izin Mendirikan Bangunan an. WARTA SUGIRA</t>
-  </si>
-  <si>
-    <t>02</t>
-  </si>
-  <si>
-    <t>Nomor : 503.IT/ SK. 025. BPMPP/2010. an Witana</t>
-  </si>
-  <si>
-    <t>03</t>
-  </si>
-  <si>
-    <t>Nomor : 503. IG/SK. 085-BPMPP/2011. Tentang Izin Gangguan an. Ir WIRANTO.M.Si</t>
-  </si>
-  <si>
-    <t>04</t>
-  </si>
-  <si>
-    <t>Nomor : 503. Pan/ Herr. 006-BPMPP/ 2009. Tentang IzinUsaha Kepariwisataan an. WIWIN WINARTI</t>
-  </si>
-  <si>
-    <t>05</t>
-  </si>
-  <si>
-    <t>Nomor : 503. IMB/ SK. 120/ BPMPP/ 2011 Tentang IMB an. HJ. YUYU YUSANTI</t>
-  </si>
-  <si>
-    <t>Nomor : 503 : IMB/ SK.174/BPMPP/ 2011.Tentang IMB an. YOYO SUTARYO</t>
-  </si>
-  <si>
-    <t>Nomor : 503.IMB/ SK.153/ BPMPP/ 2011. Tentang IMB an. YADI SUKMAYADI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nomor : 503. IMB/ SK.154/ BPMPP/ 2011.Tentang IMB an. YANSOMA </t>
-  </si>
-  <si>
-    <t>Nomor : 503. IG/ SK. 165-BPMPP/ 2011. Tentang Ijin Gangguan an. YAYAN SAEFUDIN</t>
-  </si>
-  <si>
-    <t>Depo Baru</t>
   </si>
 </sst>
 </file>
@@ -143,7 +109,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -192,31 +158,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -236,42 +182,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -282,6 +203,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -330,7 +254,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -365,7 +289,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -574,17 +498,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:L3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.5546875" customWidth="1"/>
+    <col min="1" max="1" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>11</v>
       </c>
@@ -614,7 +538,7 @@
       </c>
       <c r="L1" s="3"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="6"/>
       <c r="C2" s="3"/>
@@ -640,310 +564,33 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" s="9">
+    <row r="3" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="8">
         <v>500</v>
       </c>
-      <c r="C3" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="11" t="s">
+      <c r="C3" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="9">
+      <c r="D3" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="8">
         <v>2011</v>
       </c>
-      <c r="F3" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="8" t="s">
+      <c r="F3" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" s="12"/>
-      <c r="K3" s="13"/>
-      <c r="L3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="7">
-        <v>1</v>
-      </c>
-      <c r="B4" s="15">
-        <v>500</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="17" t="s">
+      <c r="G3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="15">
-        <v>2011</v>
-      </c>
-      <c r="F4" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="I4" s="14"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="7">
-        <v>1</v>
-      </c>
-      <c r="B5" s="15">
-        <v>500</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" s="15">
-        <v>2010</v>
-      </c>
-      <c r="F5" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="14"/>
-      <c r="H5" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="I5" s="14"/>
-      <c r="J5" s="18"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="7">
-        <v>1</v>
-      </c>
-      <c r="B6" s="15">
-        <v>500</v>
-      </c>
-      <c r="C6" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="15">
-        <v>2011</v>
-      </c>
-      <c r="F6" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="I6" s="14"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="19"/>
-      <c r="L6" s="7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="7">
-        <v>1</v>
-      </c>
-      <c r="B7" s="15">
-        <v>500</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="15">
-        <v>2009</v>
-      </c>
-      <c r="F7" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="I7" s="14"/>
-      <c r="J7" s="18"/>
-      <c r="K7" s="19"/>
-      <c r="L7" s="7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A8" s="7">
-        <v>1</v>
-      </c>
-      <c r="B8" s="15">
-        <v>500</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" s="15">
-        <v>2011</v>
-      </c>
-      <c r="F8" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="G8" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="H8" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="I8" s="14"/>
-      <c r="J8" s="18"/>
-      <c r="K8" s="19"/>
-      <c r="L8" s="7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A9" s="7">
-        <v>1</v>
-      </c>
-      <c r="B9" s="15">
-        <v>500</v>
-      </c>
-      <c r="C9" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" s="15">
-        <v>2001</v>
-      </c>
-      <c r="F9" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="I9" s="15"/>
-      <c r="J9" s="18"/>
-      <c r="K9" s="19"/>
-      <c r="L9" s="7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A10" s="7">
-        <v>1</v>
-      </c>
-      <c r="B10" s="15">
-        <v>500</v>
-      </c>
-      <c r="C10" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="E10" s="15">
-        <v>2011</v>
-      </c>
-      <c r="F10" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="I10" s="15"/>
-      <c r="J10" s="18"/>
-      <c r="K10" s="19"/>
-      <c r="L10" s="7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A11" s="7">
-        <v>1</v>
-      </c>
-      <c r="B11" s="15">
-        <v>500</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="D11" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="E11" s="15">
-        <v>2011</v>
-      </c>
-      <c r="F11" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="I11" s="15"/>
-      <c r="J11" s="18"/>
-      <c r="K11" s="19"/>
-      <c r="L11" s="7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A12" s="7">
-        <v>1</v>
-      </c>
-      <c r="B12" s="15">
-        <v>500</v>
-      </c>
-      <c r="C12" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="E12" s="15">
-        <v>2011</v>
-      </c>
-      <c r="F12" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="I12" s="15"/>
-      <c r="J12" s="18"/>
-      <c r="K12" s="19"/>
-      <c r="L12" s="7" t="s">
-        <v>31</v>
+      <c r="H3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -964,7 +611,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -973,7 +620,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
